--- a/important_mails_2026-10-02.xlsx
+++ b/important_mails_2026-10-02.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Fri, 2 Oct 2026 08:41:07 +0000</t>
+          <t>Fri, 2 Oct 2026 17:14:32 +0000</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -610,11 +610,156 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Zmiana kategorii opłat obowiązująca od 31 października 2026 r.</t>
+          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
+ Dzień dobry Weihai EU,
+ niektóre z Twoich ofert zostały zdezaktywowane z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
+ Dlaczego tak się stało?
+ Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami . Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
+ Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
+ Jak mogę ponownie aktywować oferty?
+ Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 2 Oct 2026 16:48:36 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
+ le offerte</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
+ Gentile Weihai EU,
+ Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
+ Ciò a cosa è dovuto?
+ Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
+ La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
+ Come faccio a riattivare le mie offerte?
+ Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
+-
+ Se disponi della documentazione richiesta, segui le istruzioni per inviare i do</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 2 Oct 2026 16:38:58 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Austrian Parcel Tax now in effect</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amazon Services
+ 96
+ No action required. We’ll pay the tax to the Austrian Tax Authority
+ Hello,
+ As of October 1, 2026, Austria’s Parcel Tax Act (Paketsteuergesetz, PakStG) is in effect. As previously communicated, the law introduces a €2.00 flat tax per order on all Business-to-Consumer (B2C) orders delivered to customers in Austria.
+ The tax is mandated under Austrian law, and applies to both Fulfilment by Amazon (FBA) and Fulfilment by Merchant (FBM) orders from our France, Germany, Italy, Spain, or United Kingdom stores.
+ No action is required from you. We’ll pay the tax to the Austrian Tax Authority.
+ How the tax is charged
+ The tax is charged once per order at checkout, regardless of the number of items in the order, or number of packages the order arrives in. The total amount is €2.40 per order (€2.00 tax, plus 20% Austrian VAT).
+ Business-to-Business (B2B) orders made by business customers (including Amazon Business customers) with a valid Austrian or EU VAT Registration Number (VRN) are exempt from the tax.
+ Note : For recurring Subscribe &amp; Save deliveries, nothing changes for the customer at the moment and subscriptions continue as usual.
+ How customers will see the tax
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 2 Oct 2026 08:41:07 +0000</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Zmiana kategorii opłat obowiązująca od 31 października 2026 r.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Zmiana kategorii opłat w przypadku niektórych Twoich produktów w europejskich sklepach Amazon
@@ -628,39 +773,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 07:57:37 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Actualización de las categorías de tarifas con entrada en vigor el 31 de octubre de 2026</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
  Se asignarán algunos de tus ASIN a otra categoría de tarifa en nuestras tiendas europeas.
@@ -674,39 +819,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 07:49:32 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Categorie di commissioni aggiornate dal 31 ottobre 2026</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
  Alcuni dei tuoi ASIN verranno assegnati a una categoria di commissioni diversa nei nostri negozi europei
@@ -719,39 +864,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 07:46:36 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Update van kostencategorieën, met ingang van 31 oktober 2026</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
  Enkele van je ASIN-codes worden toegewezen aan een andere kostencategorie in onze Europese winkels
@@ -764,39 +909,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 19:30:09 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (4sQeBGpWIe)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -816,39 +961,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 09:21:47 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -864,39 +1009,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 05:14:04 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -912,39 +1057,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 05:02:53 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -960,39 +1105,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 23:20:30 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cENUYoUvou)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1017,39 +1162,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 04:48:00 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1065,39 +1210,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 16:39:11 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1118,39 +1263,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 14:51:16 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -1166,39 +1311,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 13:36:40 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1218,39 +1363,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 13:33:11 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1270,39 +1415,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 00:41:51 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1322,39 +1467,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Wed, 30 Sep 2026 10:06:35 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -1372,39 +1517,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 10:06:26 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -1422,39 +1567,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 05:31:39 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>重要通知｜9月1日起，Pan-EU入库欧盟及直接发往法国的货件必须提供进口详情</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>未提供 MRN+EORI 将无法创建新货件，请在收货后 60 天内完成补全
 尊敬的 深圳市微海众信科技有限公司,
@@ -1482,39 +1627,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 10:05:46 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -1533,39 +1678,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 10:05:10 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -1584,39 +1729,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:10:33 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1634,39 +1779,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:07:50 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1684,39 +1829,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 02:30:17 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 09/2026</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -1734,39 +1879,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Wed, 30 Sep 2026 08:58:18 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>You’ve been enrolled in EPR Pay on Behalf for Amazon.co.uk</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">You’ve been enrolled in EPR Pay on Behalf for Amazon.co.uk
  96
@@ -1776,39 +1921,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 05:54:05 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Transparency No Reply &lt;noreply-transparency@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>OPR 体验优化——无需再手动追踪货件  /  Improvement to Your OPR Experience — No More Manual Shipment Tracking</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>尊敬的 Mzyxxel 团队：
 我们很高兴地通知您，OPR（Operational Performance Review运营表现评估）流程迎来一项优化，这将使开启 OPR 变得更加简单，并且您无需再手动追踪货件。
@@ -1832,39 +1977,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:10:17 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -1880,40 +2025,40 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:09:41 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -1929,39 +2074,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:09:40 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -1975,40 +2120,40 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:09:39 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -2024,39 +2169,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:09:28 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -2072,39 +2217,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:08:10 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -2120,39 +2265,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 00:44:41 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -2168,39 +2313,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 04:55:34 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2223,39 +2368,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 04:10:17 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-08</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2279,39 +2424,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 21:27:08 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>A passkey is required for account access starting in two weeks</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  For security, set up passkey login to maintain account access
@@ -2327,39 +2472,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 04:58:43 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>A returns experience customers actually like</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Faster resolutions for buyers, less friction for you.
@@ -2384,39 +2529,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 00:17:41 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>View your US Q4-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q4-2026
@@ -2446,39 +2591,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Fri, 25 Sep 2026 04:50:51 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2494,39 +2639,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 04:54:38 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2542,39 +2687,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 16:43:27 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7iKN0D3u4y)</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2594,39 +2739,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 09:25:48 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2642,39 +2787,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 05:04:18 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2690,39 +2835,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 14:06:30 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Address variation policy violations</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Address variation policy violations
@@ -2738,39 +2883,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 04:54:44 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2786,39 +2931,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sun, 20 Sep 2026 14:23:10 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -2841,39 +2986,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sat, 19 Sep 2026 04:50:14 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2889,39 +3034,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Fri, 18 Sep 2026 05:13:12 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2937,39 +3082,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 04:57:09 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2985,39 +3130,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 07:03:28 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3033,39 +3178,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 09:36:39 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3081,39 +3226,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sun, 13 Sep 2026 04:42:34 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3129,39 +3274,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 04:52:40 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3177,39 +3322,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 09:37:22 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3225,39 +3370,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 05:39:06 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3273,39 +3418,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 09:08:38 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3321,39 +3466,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 05:04:40 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3369,39 +3514,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 11:29:22 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (YHD3zckrc9)</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3421,39 +3566,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 09:22:19 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3469,39 +3614,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 04:57:55 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3517,39 +3662,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 11:28:14 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (pWbU6lC/+G)</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3569,39 +3714,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:54:29 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3617,39 +3762,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 04:38:47 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3665,39 +3810,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 09:20:41 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3713,39 +3858,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 17:54:07 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (4rjrNkqMZx)</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3765,39 +3910,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 05:00:38 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3810,163 +3955,6 @@
 - In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
 - To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
 -</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 2 Sep 2026 10:49:16 +0000</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (j2jHyzbiUU)</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-8310203-8288062
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-1618482804949060</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 2 Sep 2026 04:50:31 +0000</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 1 Sep 2026 19:31:35 +0000</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (TrF4EN0N6o)</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-Disposal Summary:
-Quantity Requested: 1
-Quantity Successfully Destroyed: 1
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-3466953-4664826
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-457399084289619</t>
         </is>
       </c>
     </row>
@@ -12848,7 +12836,7 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>货件/库存类</t>
+          <t>其他风险类</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -12863,65 +12851,21 @@
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Wed, 2 Sep 2026 13:15:30 +0000</t>
+          <t>Wed, 23 Sep 2026 10:37:18 +0800 (CST)</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+          <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>Stranded SKUs scheduled for automatic removal</t>
+          <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr"/>
       <c r="H243" s="2" t="inlineStr">
-        <is>
-          <t>96
-Stranded SKUs scheduled for automatic removal
- Hello,
- You are receiving this message because you have stranded inventory in an Amazon fulfilment centre that is scheduled for automatic removal. Stranded inventory is inventory without a buyable offer and requires you to either reactivate the listing or remove the inventory.
- As of 2026-09-02, you have 1 new stranded SKUs scheduled for automatic removal, with the first 50 of these listed further below. You may have additional units scheduled for automatic removal from previous email notifications. For a full view of units scheduled for automatic removal, visit Fix stranded inventory and sort by Automatic Removal date .
- Your inventory will be returned or disposed of based on the settings you selected on the Fix stranded inventory page. If you have not selected any settings, your inventory will be removed in 60 days from today’s date. To customise your settings, go to Fix stranded inventory and select Edit automatic-action settings .
- If you need more time to appeal or fix a stranded inventory issue, go to Fix stranded inventory and select Delay removal for 30 days from the drop-down menu for each listing. Note: No additional notif</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 23 Sep 2026 10:37:18 +0800 (CST)</t>
-        </is>
-      </c>
-      <c r="E244" s="2" t="inlineStr">
-        <is>
-          <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
-        </is>
-      </c>
-      <c r="F244" s="2" t="inlineStr">
-        <is>
-          <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
-        </is>
-      </c>
-      <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -12950,39 +12894,39 @@
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 01:44:18 +0000</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr"/>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -13004,39 +12948,39 @@
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>Tue, 22 Sep 2026 10:57:46 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -13064,40 +13008,40 @@
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 21:52:15 +0000</t>
         </is>
       </c>
-      <c r="E247" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>FBA Grade and Resell is now Sell as Used and includes refurbished
  items</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr"/>
-      <c r="H247" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>96
  Recover more value from your eligible FBA returns.
@@ -13112,39 +13056,39 @@
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>Mon, 21 Sep 2026 10:15:39 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E248" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F248" s="2" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr"/>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -13172,39 +13116,39 @@
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>Thu, 17 Sep 2026 13:51:44 +0000</t>
         </is>
       </c>
-      <c r="E249" s="2" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfilment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F249" s="2" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>Your peak prep checklist is ready</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr"/>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>Your peak prep checklist is ready
 Position inventory, activate savings, and make your delivery speed visible. ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌ ‌
@@ -13220,39 +13164,39 @@
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:31:48 +0000</t>
         </is>
       </c>
-      <c r="E250" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F250" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr"/>
-      <c r="H250" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -13275,39 +13219,39 @@
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 10:27:49 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E251" s="2" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F251" s="2" t="inlineStr">
+      <c r="F250" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr"/>
-      <c r="H251" s="2" t="inlineStr">
+      <c r="G250" s="2" t="inlineStr"/>
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -13335,39 +13279,39 @@
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 14:01:06 +0000</t>
         </is>
       </c>
-      <c r="E252" s="2" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F252" s="2" t="inlineStr">
+      <c r="F251" s="2" t="inlineStr">
         <is>
           <t>Redesigned Seller Central becomes default 24 Sep</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr"/>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>96
  Same powerful tools, built to grow with your business.
@@ -13382,40 +13326,40 @@
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 03:24:54 +0000</t>
         </is>
       </c>
-      <c r="E253" s="2" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Communications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F253" s="2" t="inlineStr">
+      <c r="F252" s="2" t="inlineStr">
         <is>
           <t>[Amazon.fr] One or More of Your Amazon Listings Have Been Search
  Suppressed</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr"/>
-      <c r="H253" s="2" t="inlineStr">
+      <c r="G252" s="2" t="inlineStr"/>
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>96
 [Amazon.fr] One or More of Your Amazon Listings Have Been Search Suppressed
